--- a/7_Data_Extraction/Data_Extraction_Dario.xlsx
+++ b/7_Data_Extraction/Data_Extraction_Dario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://communitystudentiunina.sharepoint.com/sites/PRINMEDITATE/Shared Documents/SLR/RegressionTestingOptimizationSLR/7_Data_Extraction/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniotrovato/Documents/GitHub/RegressionTestingOptimizationSLR/7_Data_Extraction/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="402" documentId="13_ncr:1_{99B88D9A-5E7C-4742-9EEF-BFEDDFFF5C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4406B9-072D-7A4B-AD0E-F6A1D6FE6CF3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D445C8-7169-CD4F-BCEA-E7D77B9174B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2063,6 +2063,9 @@
       <c r="AN5" s="8" t="s">
         <v>59</v>
       </c>
+      <c r="AW5" s="7">
+        <v>0</v>
+      </c>
       <c r="AX5" s="7" t="s">
         <v>297</v>
       </c>
@@ -2177,6 +2180,9 @@
       </c>
       <c r="AN7" s="8" t="s">
         <v>59</v>
+      </c>
+      <c r="AW7" s="7">
+        <v>0</v>
       </c>
       <c r="AX7" s="7" t="s">
         <v>297</v>
@@ -2820,6 +2826,9 @@
       </c>
       <c r="AN16" s="8" t="s">
         <v>59</v>
+      </c>
+      <c r="AW16" s="7">
+        <v>0</v>
       </c>
       <c r="AX16" s="7" t="s">
         <v>297</v>

--- a/7_Data_Extraction/Data_Extraction_Dario.xlsx
+++ b/7_Data_Extraction/Data_Extraction_Dario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniotrovato/Documents/GitHub/RegressionTestingOptimizationSLR/7_Data_Extraction/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D445C8-7169-CD4F-BCEA-E7D77B9174B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0779C755-2D3F-6145-899A-728188653790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="1300" windowWidth="28800" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="380">
   <si>
     <t>ID</t>
   </si>
@@ -763,15 +763,6 @@
   </si>
   <si>
     <t>Test-case prioritization, proposed at the end of last century, aims to schedule the execution order of test cases so as to improve test effectiveness. In the past years, test-case prioritization has gained much attention, and has significant achievements in five aspects: prioritization algorithms, coverage criteria, measurement, practical concerns involved, and application scenarios. In this article, we will first review the achievements of test-case prioritization from these five aspects and then give our perspectives on its challenges.</t>
-  </si>
-  <si>
-    <t>R Mukherjee, KS Patnaik</t>
-  </si>
-  <si>
-    <t>Journal of King Saud University-Computer and Information Sciences, 2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> A survey on different approaches for software test case prioritization</t>
   </si>
   <si>
     <t>O Dahiya, K Solanki</t>
@@ -819,15 +810,6 @@
 The solution delivers optimal results in pseudo-polynomial time complexity, is effective for amounts of test cases up to the order of millions and compared with the classical dynamic programming methods leads to higher number of test cases to be involved in the selection process due to reduced memory consumption.</t>
   </si>
   <si>
-    <t>MJ Arafeen, H Do</t>
-  </si>
-  <si>
-    <t>Test case prioritization using requirements-based clustering</t>
-  </si>
-  <si>
-    <t>The importance of using requirements information in the testing phase has been well recognized by the requirements engineering community, but to date, a vast majority of regression testing techniques have primarily relied on software code information. Incorporating requirements information into the current testing practice could help software engineers identify the source of defects more easily, validate the product against requirements, and maintain software products in a holistic way. In this paper, we investigate whether the requirements-based clustering approach that incorporates traditional code analysis information can improve the effectiveness of test case prioritization techniques. To investigate the effectiveness of our approach, we performed an empirical study using two Java programs with multiple versions and requirements documents. Our results indicate that the use of requirements information during the test case prioritization process can be beneficial.</t>
-  </si>
-  <si>
     <t>Christopher Henard, Mike Papadakis, Mark Harman, Yue Jia, Yves Le Traon</t>
   </si>
   <si>
@@ -1168,25 +1150,7 @@
     <t>memory consumption</t>
   </si>
   <si>
-    <t>1. 2013; 2. Prioritization</t>
-  </si>
-  <si>
-    <t>Requirement-based</t>
-  </si>
-  <si>
     <t>An industrial case study</t>
-  </si>
-  <si>
-    <t>Two systems</t>
-  </si>
-  <si>
-    <t>6.82 to 30.30 KLOC, 42 to 142 test cases</t>
-  </si>
-  <si>
-    <t>Clustering methods</t>
-  </si>
-  <si>
-    <t>Requirement-test case traceability matrix</t>
   </si>
   <si>
     <t>APFD and Jaccard coefficient</t>
@@ -1644,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AX30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
@@ -1816,7 +1780,7 @@
         <v>48</v>
       </c>
       <c r="AX1" s="10" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:50" ht="48" x14ac:dyDescent="0.2">
@@ -1860,25 +1824,25 @@
         <v>59</v>
       </c>
       <c r="AO2" s="7" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AP2" s="7" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AQ2" s="7" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AS2" s="7" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AT2" s="7" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AU2" s="7" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AV2" s="7" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AW2" s="7">
         <v>0</v>
@@ -1928,28 +1892,28 @@
         <v>59</v>
       </c>
       <c r="AO3" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="AP3" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="AQ3" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="AR3" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="AS3" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="AT3" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="AP3" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="AQ3" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="AR3" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="AS3" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="AT3" s="7" t="s">
-        <v>288</v>
-      </c>
       <c r="AU3" s="7" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="AV3" s="7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AW3" s="7">
         <v>0</v>
@@ -1996,25 +1960,25 @@
         <v>59</v>
       </c>
       <c r="AO4" s="7" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="AP4" s="7" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AQ4" s="7" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AS4" s="7" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="AT4" s="7" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AU4" s="7" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AV4" s="7" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="AW4" s="7">
         <v>0</v>
@@ -2067,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="AX5" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:50" ht="48" x14ac:dyDescent="0.2">
@@ -2117,28 +2081,28 @@
         <v>59</v>
       </c>
       <c r="AO6" s="7" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AP6" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ6" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="AR6" s="7" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AS6" s="11" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AT6" s="7" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="AU6" s="7" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AV6" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AW6" s="7">
         <v>0.5</v>
@@ -2185,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="AX7" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:50" ht="32" x14ac:dyDescent="0.2">
@@ -2247,25 +2211,25 @@
         <v>59</v>
       </c>
       <c r="AO8" s="7" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="AP8" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ8" s="7" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AS8" s="7" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="AT8" s="7" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AU8" s="7" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AV8" s="7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AW8" s="7">
         <v>0</v>
@@ -2321,7 +2285,7 @@
         <v>132</v>
       </c>
       <c r="AO9" s="7" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AP9" s="12" t="s">
         <v>225</v>
@@ -2381,28 +2345,28 @@
         <v>59</v>
       </c>
       <c r="AO10" s="7" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AP10" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ10" s="7" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="AR10" s="7" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AS10" s="7" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AT10" s="7" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AU10" s="7" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AV10" s="7" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AW10" s="7">
         <v>0</v>
@@ -2455,25 +2419,25 @@
         <v>59</v>
       </c>
       <c r="AO11" s="7" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AP11" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ11" s="7" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AS11" s="7" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AT11" s="7" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="AU11" s="7" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="AV11" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="AW11" s="7">
         <v>0</v>
@@ -2529,28 +2493,28 @@
         <v>59</v>
       </c>
       <c r="AO12" s="7" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AP12" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="AQ12" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="AR12" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="AS12" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="AT12" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="AU12" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="AQ12" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="AR12" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="AS12" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="AT12" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="AU12" s="7" t="s">
-        <v>322</v>
-      </c>
       <c r="AV12" s="7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AW12" s="7">
         <v>0.5</v>
@@ -2603,28 +2567,28 @@
         <v>59</v>
       </c>
       <c r="AO13" s="7" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AP13" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ13" s="7" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AR13" s="7" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AS13" s="7" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AT13" s="7" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AU13" s="7" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AV13" s="7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AW13" s="7">
         <v>0</v>
@@ -2677,28 +2641,28 @@
         <v>59</v>
       </c>
       <c r="AO14" s="7" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="AP14" s="7" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="AQ14" s="7" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AR14" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="AS14" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="AT14" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="AU14" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="AS14" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="AT14" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="AU14" s="7" t="s">
-        <v>291</v>
-      </c>
       <c r="AV14" s="7" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AW14" s="7">
         <v>0.5</v>
@@ -2751,28 +2715,28 @@
         <v>59</v>
       </c>
       <c r="AO15" s="7" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AP15" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ15" s="7" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AR15" s="7" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AS15" s="7" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="AT15" s="7" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="AU15" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="AV15" s="7" t="s">
         <v>323</v>
-      </c>
-      <c r="AV15" s="7" t="s">
-        <v>329</v>
       </c>
       <c r="AW15" s="7">
         <v>1</v>
@@ -2831,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="AX16" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="1:50" ht="48" x14ac:dyDescent="0.2">
@@ -2881,28 +2845,28 @@
         <v>59</v>
       </c>
       <c r="AO17" s="7" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AP17" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ17" s="7" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AR17" s="7" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AS17" s="7" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="AT17" s="7" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AU17" s="7" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AV17" s="7" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AW17" s="7">
         <v>1</v>
@@ -2955,28 +2919,28 @@
         <v>59</v>
       </c>
       <c r="AO18" s="7" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AP18" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ18" s="7" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AR18" s="7" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AS18" s="7" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AT18" s="7" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AU18" s="7" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AV18" s="7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AW18" s="7">
         <v>1</v>
@@ -3002,7 +2966,7 @@
         <v>225</v>
       </c>
       <c r="AO19" s="7" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AP19" s="12" t="s">
         <v>225</v>
@@ -3035,28 +2999,28 @@
         <v>59</v>
       </c>
       <c r="AO20" s="7" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="AP20" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ20" s="7" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AR20" s="7" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AS20" s="7" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="AT20" s="7" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AU20" s="7" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AV20" s="7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AW20" s="7">
         <v>0</v>
@@ -3082,28 +3046,28 @@
         <v>59</v>
       </c>
       <c r="AO21" s="7" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AP21" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ21" s="7" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AR21" s="7" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AS21" s="7" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AT21" s="7" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AU21" s="7" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AV21" s="7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AW21" s="7">
         <v>0</v>
@@ -3129,34 +3093,34 @@
         <v>59</v>
       </c>
       <c r="AO22" s="7" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AP22" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ22" s="7" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AR22" s="7" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AS22" s="7" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="AT22" s="7" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AU22" s="7" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="AV22" s="7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AW22" s="7">
         <v>1</v>
       </c>
       <c r="AX22" s="7" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="23" spans="1:50" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -3179,7 +3143,7 @@
         <v>132</v>
       </c>
       <c r="AO23" s="7" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AP23" s="12" t="s">
         <v>132</v>
@@ -3206,16 +3170,16 @@
         <v>2018</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>125</v>
+        <v>245</v>
       </c>
       <c r="AN24" s="8" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="AO24" s="7" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="AP24" s="12" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="AQ24" s="12"/>
       <c r="AR24" s="12"/>
@@ -3227,220 +3191,220 @@
     </row>
     <row r="25" spans="1:50" ht="32" x14ac:dyDescent="0.2">
       <c r="C25" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F25" s="5">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN25" s="8" t="s">
-        <v>225</v>
+        <v>59</v>
       </c>
       <c r="AO25" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="AP25" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="AQ25" s="12"/>
-      <c r="AR25" s="12"/>
-      <c r="AS25" s="12"/>
-      <c r="AT25" s="12"/>
-      <c r="AU25" s="12"/>
-      <c r="AV25" s="12"/>
-      <c r="AW25" s="12"/>
+        <v>276</v>
+      </c>
+      <c r="AP25" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="AQ25" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="AR25" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="AS25" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="AT25" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="AU25" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="AV25" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="AW25" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="AX25" s="7" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="26" spans="1:50" ht="32" x14ac:dyDescent="0.2">
       <c r="C26" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F26" s="5">
         <v>2019</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN26" s="8" t="s">
         <v>59</v>
       </c>
       <c r="AO26" s="7" t="s">
-        <v>282</v>
+        <v>362</v>
       </c>
       <c r="AP26" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="AQ26" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="AQ26" s="7" t="s">
+      <c r="AR26" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="AS26" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="AR26" s="7" t="s">
+      <c r="AT26" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="AU26" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="AS26" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="AT26" s="7" t="s">
+      <c r="AV26" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="AU26" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="AV26" s="7" t="s">
-        <v>362</v>
-      </c>
       <c r="AW26" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="AX26" s="7" t="s">
-        <v>366</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:50" ht="96" x14ac:dyDescent="0.2">
       <c r="C27" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F27" s="5">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN27" s="8" t="s">
         <v>59</v>
       </c>
       <c r="AO27" s="7" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="AP27" s="7" t="s">
-        <v>361</v>
+        <v>277</v>
       </c>
       <c r="AQ27" s="7" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AR27" s="7" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AS27" s="7" t="s">
         <v>369</v>
       </c>
       <c r="AT27" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AU27" s="7" t="s">
-        <v>291</v>
+        <v>371</v>
       </c>
       <c r="AV27" s="7" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AW27" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:50" ht="32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="C28" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F28" s="5">
         <v>2013</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN28" s="8" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="AO28" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="AP28" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="AQ28" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="AR28" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="AS28" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="AT28" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="AU28" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="AV28" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="AW28" s="7">
-        <v>0</v>
-      </c>
+      <c r="AP28" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="AQ28" s="12"/>
+      <c r="AR28" s="12"/>
+      <c r="AS28" s="12"/>
+      <c r="AT28" s="12"/>
+      <c r="AU28" s="12"/>
+      <c r="AV28" s="12"/>
+      <c r="AW28" s="12"/>
     </row>
-    <row r="29" spans="1:50" ht="96" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:50" ht="48" x14ac:dyDescent="0.2">
       <c r="C29" s="7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F29" s="5">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AN29" s="8" t="s">
         <v>59</v>
       </c>
       <c r="AO29" s="7" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="AP29" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AQ29" s="7" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="AR29" s="7" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="AS29" s="7" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="AT29" s="7" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="AU29" s="7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AV29" s="7" t="s">
         <v>379</v>
@@ -3449,30 +3413,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:50" ht="32" x14ac:dyDescent="0.2">
       <c r="C30" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F30" s="5">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN30" s="8" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="AO30" s="7" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="AP30" s="12" t="s">
-        <v>386</v>
+        <v>225</v>
       </c>
       <c r="AQ30" s="12"/>
       <c r="AR30" s="12"/>
@@ -3482,95 +3446,14 @@
       <c r="AV30" s="12"/>
       <c r="AW30" s="12"/>
     </row>
-    <row r="31" spans="1:50" ht="48" x14ac:dyDescent="0.2">
-      <c r="C31" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="F31" s="5">
-        <v>2014</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="AN31" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="AO31" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="AP31" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="AQ31" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="AR31" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="AS31" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="AT31" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="AU31" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="AV31" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="AW31" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:50" ht="32" x14ac:dyDescent="0.2">
-      <c r="C32" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="F32" s="5">
-        <v>2017</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="AN32" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="AO32" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="AP32" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="AQ32" s="12"/>
-      <c r="AR32" s="12"/>
-      <c r="AS32" s="12"/>
-      <c r="AT32" s="12"/>
-      <c r="AU32" s="12"/>
-      <c r="AV32" s="12"/>
-      <c r="AW32" s="12"/>
-    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="AP9:AW9"/>
     <mergeCell ref="AP19:AW19"/>
-    <mergeCell ref="AP25:AW25"/>
-    <mergeCell ref="AP32:AW32"/>
-    <mergeCell ref="AP23:AW23"/>
     <mergeCell ref="AP24:AW24"/>
     <mergeCell ref="AP30:AW30"/>
+    <mergeCell ref="AP23:AW23"/>
+    <mergeCell ref="AP28:AW28"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
@@ -3602,6 +3485,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="ab92c565-5003-4ac3-93a3-a3ce8796a3c0">
@@ -3610,15 +3502,6 @@
     <TaxCatchAll xmlns="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3817,6 +3700,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91C10C48-AAE1-45D5-AD1E-921FB09E3C0B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23090AFA-087E-44CC-9E33-A4FB55B7B01B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -3829,14 +3720,6 @@
     <ds:schemaRef ds:uri="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91C10C48-AAE1-45D5-AD1E-921FB09E3C0B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
